--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1595,324 +1726,259 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">능계가락 — 민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">능계가락</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="18"/>
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南南</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="19"/>
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一</t>
         </is>
       </c>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="19"/>
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="21"/>
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="18"/>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="19"/>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一</t>
         </is>
       </c>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="19"/>
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一△</t>
         </is>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" s="22"/>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一△</t>
         </is>
       </c>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑南</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="23"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="19"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="19"/>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="21"/>
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" s="18"/>
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一仲</t>
         </is>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C16" s="20"/>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一仲</t>
         </is>
       </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="19"/>
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一△</t>
         </is>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" s="22"/>
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">一△</t>
         </is>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="I7" s="3"/>
@@ -766,13 +766,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1050,13 +1050,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1735,7 +1735,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="2"/>
@@ -1799,7 +1799,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="E8" s="3"/>
@@ -1816,7 +1816,7 @@
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E9" s="2"/>
@@ -1825,7 +1825,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1922,13 +1922,13 @@
       <c r="A16" s="0"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="E16" s="2"/>
@@ -1945,7 +1945,7 @@
       <c r="D17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E17" s="2"/>
@@ -1960,7 +1960,7 @@
       <c r="C18" s="3"/>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E18" s="2"/>

--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1699,271 +1728,271 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">능계가락</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 南</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="22"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 㴌</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="22"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="24"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="C8" s="22"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="22"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="22"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 潢無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="24"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="22"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="22"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="22"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="22"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="22"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="22"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="24"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -1717,16 +1717,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="E8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="E10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -222,6 +227,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1745,14 +1756,14 @@
 南</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -1761,13 +1772,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -1777,14 +1788,14 @@
 㴌</t>
         </is>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="E5" s="22"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -1793,13 +1804,13 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -1809,14 +1820,14 @@
 無南</t>
         </is>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -1825,13 +1836,13 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C8" s="22"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -1841,14 +1852,14 @@
 仲姑</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -1858,13 +1869,13 @@
 △</t>
         </is>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -1874,14 +1885,14 @@
 南</t>
         </is>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 潢無</t>
         </is>
       </c>
-      <c r="E11" s="22"/>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -1890,13 +1901,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -1906,14 +1917,14 @@
 無南</t>
         </is>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無南</t>
         </is>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -1922,13 +1933,13 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="25"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
@@ -1938,14 +1949,14 @@
 仲姑</t>
         </is>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
@@ -1954,13 +1965,13 @@
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
@@ -1970,14 +1981,14 @@
 △</t>
         </is>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="25"/>
     </row>
     <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
@@ -1986,13 +1997,13 @@
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C18" s="24"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E18" s="22"/>
+      <c r="E18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,19 +215,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -305,7 +306,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/4 / 16정간</t>
+          <t xml:space="preserve">4/4 / 8정간</t>
         </is>
       </c>
     </row>
@@ -329,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>
@@ -365,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -375,7 +376,11 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 25%, 박자 근사</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -401,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽 여백에 세로로 손글씨 "능계가락 신방곡". 16정간 인쇄 양식, 한 칸에 정간 2개(칸 위=홀수, 아래=짝수), 굵은 선 2칸마다 → 2/4·16. 오른쪽부터 줄1, 줄2. 줄3 이하(왼쪽 열들)는 빈 격자. 하단 양식 번호 "- 196 -"(16정간 용지). 율명 옆 좁은 가사 칸은 비어 있어 가사는 비움. 한 높이에 나란히 쓴 두 율명은 왼쪽→오른쪽 순으로 적음. 古 모양: 女변 있으면 姑, 없으면 南.</t>
+          <t xml:space="preserve">오른쪽 여백에 세로로 손글씨 "능계가락 신방곡". 16정간 인쇄 양식이지만 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 오른쪽부터 줄1, 줄2. 줄3 이하(왼쪽 열들)는 빈 격자. 하단 양식 번호 "- 196 -"(16정간 용지). 율명 옆 좁은 가사 칸은 비어 있어 가사는 비움. 한 높이에 나란히 쓴 두 율명은 왼쪽→오른쪽 순으로 적음. 古 모양: 女변 있으면 姑, 없으면 南.</t>
         </is>
       </c>
     </row>
@@ -589,13 +594,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|潢</t>
+          <t xml:space="preserve">無潢|潢|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-潢</t>
+潢
+–</t>
         </is>
       </c>
       <c r="I2" s="2"/>
@@ -625,12 +631,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢|無南|無潢</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢
+無南
+無潢</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -656,21 +664,26 @@
         <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無南</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無南</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無南|仲姑|–仲</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無南
+仲姑
+–仲</t>
+        </is>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲 위에 굵게 덧쓴 획 있음</t>
+        </is>
+      </c>
       <c r="K4" s="2"/>
     </row>
     <row r="5">
@@ -692,16 +705,18 @@
         <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">姑|–|△</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">姑
+–
+△</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -727,17 +742,18 @@
         <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南|仲姑</t>
+          <t xml:space="preserve">黃|潢無|㴌</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南
-仲姑</t>
+          <t xml:space="preserve">黃
+潢無
+㴌</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -763,24 +779,22 @@
         <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>3</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲 위에 굵게 덧쓴 획 있음</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無南|無潢</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無南
+無潢</t>
+        </is>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -802,17 +816,18 @@
         <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|–</t>
+          <t xml:space="preserve">無南|仲姑|–仲</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-–</t>
+          <t xml:space="preserve">無南
+仲姑
+–仲</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -838,16 +853,18 @@
         <v>8</v>
       </c>
       <c r="F9" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">姑|–|–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">姑
+–
+–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -864,26 +881,27 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃|潢無</t>
+          <t xml:space="preserve">姑仲|南|南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-潢無</t>
+          <t xml:space="preserve">姑仲
+南
+南</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -900,29 +918,35 @@
         </is>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢|㴌|㳞㴌</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+㴌
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞: 神처럼 보임; 㴌 오른쪽 끝 잘려 氵女만 보임</t>
+        </is>
+      </c>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -935,26 +959,27 @@
         </is>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無南</t>
+          <t xml:space="preserve">潢|無南|無潢</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無南</t>
+無南
+無潢</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -971,25 +996,28 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無南|仲姑|–|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">無南
+仲姑
+–
+△</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1006,30 +1034,35 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南|仲姑</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南
-仲姑</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|南|南</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+南</t>
+        </is>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 위에 덧써 검게 뭉개짐</t>
+        </is>
+      </c>
       <c r="K14" s="2"/>
     </row>
     <row r="15">
@@ -1042,25 +1075,27 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–仲</t>
+          <t xml:space="preserve">南|無南|無潢</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–仲</t>
+          <t xml:space="preserve">南
+無南
+無潢</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1077,26 +1112,27 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|–</t>
+          <t xml:space="preserve">無南|仲姑|–仲</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-–</t>
+          <t xml:space="preserve">無南
+仲姑
+–仲</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1113,614 +1149,39 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|△|ﾉ</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+△
+ﾉ</t>
+        </is>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 사선 1획</t>
+        </is>
+      </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>1</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑仲|南</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑仲
-南</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2">
-        <v>1</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2">
-        <v>1</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2">
-        <v>3</v>
-      </c>
-      <c r="F20" s="2">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢|㴌</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢
-㴌</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2">
-        <v>1</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C21" s="2">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2">
-        <v>4</v>
-      </c>
-      <c r="F21" s="2">
-        <v>2</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞㴌</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞㴌</t>
-        </is>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞: 神처럼 보임; 㴌 오른쪽 끝 잘려 氵女만 보임</t>
-        </is>
-      </c>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2">
-        <v>1</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2">
-        <v>2</v>
-      </c>
-      <c r="E22" s="2">
-        <v>5</v>
-      </c>
-      <c r="F22" s="2">
-        <v>3</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無南</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無南</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2">
-        <v>1</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2">
-        <v>6</v>
-      </c>
-      <c r="F23" s="2">
-        <v>3</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2">
-        <v>1</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2">
-        <v>7</v>
-      </c>
-      <c r="F24" s="2">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南|仲姑</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南
-仲姑</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2">
-        <v>1</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C25" s="2">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2">
-        <v>8</v>
-      </c>
-      <c r="F25" s="2">
-        <v>4</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|△</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2">
-        <v>1</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2">
-        <v>9</v>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|南</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2">
-        <v>1</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C27" s="2">
-        <v>2</v>
-      </c>
-      <c r="D27" s="2">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2">
-        <v>10</v>
-      </c>
-      <c r="F27" s="2">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I27" s="3"/>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南 위에 덧써 검게 뭉개짐</t>
-        </is>
-      </c>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2">
-        <v>1</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C28" s="2">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2">
-        <v>2</v>
-      </c>
-      <c r="E28" s="2">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2">
-        <v>6</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無南</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無南</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2">
-        <v>1</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C29" s="2">
-        <v>2</v>
-      </c>
-      <c r="D29" s="2">
-        <v>2</v>
-      </c>
-      <c r="E29" s="2">
-        <v>12</v>
-      </c>
-      <c r="F29" s="2">
-        <v>6</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2">
-        <v>1</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C30" s="2">
-        <v>2</v>
-      </c>
-      <c r="D30" s="2">
-        <v>2</v>
-      </c>
-      <c r="E30" s="2">
-        <v>13</v>
-      </c>
-      <c r="F30" s="2">
-        <v>7</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南|仲姑</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南
-仲姑</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2">
-        <v>1</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C31" s="2">
-        <v>2</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2">
-        <v>14</v>
-      </c>
-      <c r="F31" s="2">
-        <v>7</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2">
-        <v>1</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C32" s="2">
-        <v>2</v>
-      </c>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2">
-        <v>15</v>
-      </c>
-      <c r="F32" s="2">
-        <v>8</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|△</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-△</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2">
-        <v>1</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/능계가락.png</t>
-        </is>
-      </c>
-      <c r="C33" s="2">
-        <v>2</v>
-      </c>
-      <c r="D33" s="2">
-        <v>2</v>
-      </c>
-      <c r="E33" s="2">
-        <v>16</v>
-      </c>
-      <c r="F33" s="2">
-        <v>8</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">짧은 사선 1획</t>
-        </is>
-      </c>
-      <c r="K33" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
+  <autoFilter ref="A1:K17"/>
 </worksheet>
 </file>
 
@@ -1737,7 +1198,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="102.95" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1748,262 +1209,158 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="102.95" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
+南
 南</t>
         </is>
       </c>
-      <c r="C3" s="25"/>
+      <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-潢</t>
-        </is>
-      </c>
-      <c r="E3" s="25"/>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+潢
+–</t>
+        </is>
+      </c>
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" ht="102.95" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C4" s="25"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+㴌
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="C4" s="24"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢
+無南
+無潢</t>
         </is>
       </c>
       <c r="E4" s="25"/>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="102.95" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢
-㴌</t>
+          <t xml:space="preserve">潢
+無南
+無潢</t>
         </is>
       </c>
       <c r="C5" s="25"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無南</t>
-        </is>
-      </c>
-      <c r="E5" s="25"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無南
+仲姑
+–仲</t>
+        </is>
+      </c>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" ht="102.95" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞㴌</t>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無南
+仲姑
+–
+△</t>
         </is>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="E6" s="25"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+          <t xml:space="preserve">姑
+–
+△</t>
+        </is>
+      </c>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" ht="102.95" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無南</t>
-        </is>
-      </c>
-      <c r="C7" s="25"/>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+南</t>
+        </is>
+      </c>
+      <c r="C7" s="27"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南
-仲姑</t>
-        </is>
-      </c>
-      <c r="E7" s="25"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+          <t xml:space="preserve">黃
+潢無
+㴌</t>
+        </is>
+      </c>
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" ht="102.95" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢</t>
+          <t xml:space="preserve">南
+無南
+無潢</t>
         </is>
       </c>
       <c r="C8" s="25"/>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="E8" s="26"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無南
+無潢</t>
+        </is>
+      </c>
+      <c r="E8" s="25"/>
+    </row>
+    <row r="9" ht="102.95" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
-仲姑</t>
+仲姑
+–仲</t>
         </is>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">無南
+仲姑
+–仲</t>
+        </is>
+      </c>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" ht="102.95" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑
+△
+ﾉ</t>
+        </is>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–
 –</t>
         </is>
       </c>
-      <c r="E9" s="25"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E10" s="25"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-南</t>
-        </is>
-      </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-潢無</t>
-        </is>
-      </c>
-      <c r="E11" s="25"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="E12" s="25"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無南</t>
-        </is>
-      </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無南</t>
-        </is>
-      </c>
-      <c r="E13" s="25"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無潢</t>
-        </is>
-      </c>
-      <c r="E14" s="25"/>
-    </row>
-    <row r="15" ht="55.19" customHeight="1">
-      <c r="A15" s="0"/>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南
-仲姑</t>
-        </is>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無南
-仲姑</t>
-        </is>
-      </c>
-      <c r="E15" s="25"/>
-    </row>
-    <row r="16" ht="55.19" customHeight="1">
-      <c r="A16" s="0"/>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="E16" s="25"/>
-    </row>
-    <row r="17" ht="55.19" customHeight="1">
-      <c r="A17" s="0"/>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-△</t>
-        </is>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-–</t>
-        </is>
-      </c>
-      <c r="E17" s="25"/>
-    </row>
-    <row r="18" ht="55.19" customHeight="1">
-      <c r="A18" s="0"/>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E18" s="25"/>
+      <c r="E10" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2011,6 +1368,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -1184,6 +1184,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1192,10 +1195,10 @@
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="102.95" customHeight="1">
+    <row r="2" ht="52.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1206,7 +1209,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="102.95" customHeight="1">
+    <row r="3" ht="117.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1225,7 +1228,7 @@
       </c>
       <c r="E3" s="22"/>
     </row>
-    <row r="4" ht="102.95" customHeight="1">
+    <row r="4" ht="117.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -1244,7 +1247,7 @@
       </c>
       <c r="E4" s="25"/>
     </row>
-    <row r="5" ht="102.95" customHeight="1">
+    <row r="5" ht="117.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1263,7 +1266,7 @@
       </c>
       <c r="E5" s="24"/>
     </row>
-    <row r="6" ht="102.95" customHeight="1">
+    <row r="6" ht="117.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="E6" s="26"/>
     </row>
-    <row r="7" ht="102.95" customHeight="1">
+    <row r="7" ht="117.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -1302,7 +1305,7 @@
       </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" ht="102.95" customHeight="1">
+    <row r="8" ht="117.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1321,7 +1324,7 @@
       </c>
       <c r="E8" s="25"/>
     </row>
-    <row r="9" ht="102.95" customHeight="1">
+    <row r="9" ht="117.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1340,7 +1343,7 @@
       </c>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" ht="102.95" customHeight="1">
+    <row r="10" ht="117.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -1365,6 +1368,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/능계가락.xlsx
+++ b/sheets/민요/검수/능계가락.xlsx
@@ -1189,9 +1189,9 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
